--- a/SLK01D.xlsx
+++ b/SLK01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t/>
   </si>
@@ -152,12 +152,6 @@
   </si>
   <si>
     <t>PW/KARTA SP.KENCUR90</t>
-  </si>
-  <si>
-    <t>10017484</t>
-  </si>
-  <si>
-    <t>WESTON BAGELAN 100G</t>
   </si>
   <si>
     <t>20028161</t>
@@ -685,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1049,7 +1043,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>16</v>
@@ -1069,10 +1063,10 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,10 +1083,10 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,7 +1103,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
@@ -1126,13 +1120,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1149,10 +1143,10 @@
         <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1169,10 +1163,10 @@
         <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,10 +1183,10 @@
         <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,10 +1203,10 @@
         <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,18 +1223,18 @@
         <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1249,7 +1243,7 @@
         <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>20</v>
@@ -1257,10 +1251,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1269,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>20</v>
@@ -1277,19 +1271,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
@@ -1309,10 +1303,10 @@
         <v>23</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1329,7 +1323,7 @@
         <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>35</v>
@@ -1349,7 +1343,7 @@
         <v>23</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>35</v>
@@ -1369,10 +1363,10 @@
         <v>23</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,7 +1383,7 @@
         <v>23</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
@@ -1409,10 +1403,10 @@
         <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,10 +1423,10 @@
         <v>23</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1449,29 +1443,9 @@
         <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/SLK01D.xlsx
+++ b/SLK01D.xlsx
@@ -983,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>20</v>
@@ -1003,7 +1003,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>35</v>
@@ -1043,7 +1043,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>16</v>
@@ -1063,7 +1063,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>35</v>
@@ -1083,7 +1083,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
@@ -1103,7 +1103,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
